--- a/templates/INFRA ADV CLB - template.xlsx
+++ b/templates/INFRA ADV CLB - template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
@@ -1389,96 +1389,96 @@
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="27">
       <c r="B18" s="28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C18" s="29" t="n">
-        <v>133.29806416</v>
+        <v>129.88894215</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>-0.002049093680458691</v>
+        <v>0.002414961560699425</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="31" t="n">
-        <v>-3.776001123400016</v>
+        <v>4.450210184693757</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="27">
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C19" s="33" t="n">
-        <v>133.57176522</v>
+        <v>129.57602104</v>
       </c>
       <c r="D19" s="34" t="n">
-        <v>-0.004743797644160441</v>
+        <v>-0.001196439531788718</v>
       </c>
       <c r="E19" s="34" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="35" t="n">
-        <v>-8.741711227923179</v>
+        <v>-2.204758649737812</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="27">
       <c r="B20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C20" s="33" t="n">
-        <v>134.20842282</v>
+        <v>129.73123662</v>
       </c>
       <c r="D20" s="34" t="n">
-        <v>-0.0001361686606352608</v>
+        <v>-0.003389016976608539</v>
       </c>
       <c r="E20" s="34" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="35" t="n">
-        <v>-0.250927041761957</v>
+        <v>-6.245166842753116</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="27">
       <c r="B21" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C21" s="33" t="n">
-        <v>134.22670029</v>
+        <v>130.17239307</v>
       </c>
       <c r="D21" s="34" t="n">
-        <v>-0.005579593734171939</v>
+        <v>-0.005228049116312916</v>
       </c>
       <c r="E21" s="34" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="35" t="n">
-        <v>-10.28188823638006</v>
+        <v>-9.634073602710524</v>
       </c>
     </row>
     <row r="22" ht="15.95" customFormat="1" customHeight="1" s="27">
       <c r="B22" s="32" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C22" s="33" t="n">
-        <v>134.97983292</v>
+        <v>130.85651737</v>
       </c>
       <c r="D22" s="34" t="n">
-        <v>0.008309137634052055</v>
+        <v>0.002339195098887803</v>
       </c>
       <c r="E22" s="34" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F22" s="35" t="n">
-        <v>15.31180020702739</v>
+        <v>4.310590289495659</v>
       </c>
     </row>
     <row r="23" ht="15.95" customHeight="1">
@@ -1518,18 +1518,18 @@
     <row r="25" ht="15.95" customFormat="1" customHeight="1" s="27">
       <c r="B25" s="52" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C25" s="52" t="inlineStr"/>
       <c r="D25" s="30" t="n">
-        <v>-0.004817756241104809</v>
+        <v>-0.01378913217775057</v>
       </c>
       <c r="E25" s="30" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F25" s="31" t="n">
-        <v>-0.4595618971548023</v>
+        <v>-3.624116131673043</v>
       </c>
       <c r="G25" s="36" t="n"/>
     </row>
@@ -1541,13 +1541,13 @@
       </c>
       <c r="C26" s="53" t="inlineStr"/>
       <c r="D26" s="34" t="n">
-        <v>0.005296180438263631</v>
+        <v>-0.03519182429478862</v>
       </c>
       <c r="E26" s="34" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F26" s="35" t="n">
-        <v>0.4566517178962801</v>
+        <v>-3.057388152323473</v>
       </c>
       <c r="G26" s="51" t="n"/>
     </row>
@@ -1559,13 +1559,13 @@
       </c>
       <c r="C27" s="53" t="inlineStr"/>
       <c r="D27" s="34" t="n">
-        <v>0.05622031314351816</v>
+        <v>0.02772719952092118</v>
       </c>
       <c r="E27" s="34" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F27" s="35" t="n">
-        <v>1.593178804716951</v>
+        <v>0.7877346102292521</v>
       </c>
       <c r="G27" s="51" t="n"/>
     </row>
@@ -1577,13 +1577,13 @@
       </c>
       <c r="C28" s="53" t="inlineStr"/>
       <c r="D28" s="34" t="n">
-        <v>0.1568813032476342</v>
+        <v>0.1025023304923784</v>
       </c>
       <c r="E28" s="34" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F28" s="35" t="n">
-        <v>2.182913517179397</v>
+        <v>1.42810218345238</v>
       </c>
       <c r="G28" s="51" t="n"/>
     </row>
@@ -1595,13 +1595,13 @@
       </c>
       <c r="C29" s="53" t="inlineStr"/>
       <c r="D29" s="34" t="n">
-        <v>0.05151974909953494</v>
+        <v>0.02462694204194671</v>
       </c>
       <c r="E29" s="34" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F29" s="35" t="n">
-        <v>1.588202766973303</v>
+        <v>0.6471342363812903</v>
       </c>
       <c r="G29" s="51" t="n"/>
     </row>
@@ -1631,13 +1631,13 @@
       </c>
       <c r="C31" s="53" t="inlineStr"/>
       <c r="D31" s="34" t="n">
-        <v>0.3329806415999998</v>
+        <v>0.2988894215</v>
       </c>
       <c r="E31" s="34" t="n">
-        <v>0.1134063390652134</v>
+        <v>0.1194631520887273</v>
       </c>
       <c r="F31" s="35" t="n">
-        <v>2.936173095302214</v>
+        <v>2.501938181557522</v>
       </c>
       <c r="G31" s="51" t="n"/>
     </row>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="E36" s="37" t="n">
-        <v>29614054.49</v>
+        <v>28856669.71</v>
       </c>
       <c r="F36" s="37" t="n"/>
     </row>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="E37" s="37" t="n">
-        <v>30530675.05714286</v>
+        <v>30460057.15203883</v>
       </c>
       <c r="F37" s="37" t="n"/>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D39" s="46" t="n"/>
